--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2949" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2949" uniqueCount="519">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-20T17:48:12+00:00</t>
+    <t>2023-01-25T15:14:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -436,11 +436,11 @@
     <t>PertinenciaAtencionBox</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ExtBoolean}
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ExtBoolPertinenciaAtencionBox}
 </t>
   </si>
   <si>
-    <t>ExtBoolean</t>
+    <t>ExtBool Pertinencia Atencion Box</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -450,11 +450,11 @@
     <t>MotivoNoPertinencia</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ExtString}
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ExtStringMotivoNoPertinencia}
 </t>
   </si>
   <si>
-    <t>ExtString</t>
+    <t>ExtString MotivoNoPertinencia</t>
   </si>
   <si>
     <t>Encounter.modifierExtension</t>
@@ -711,6 +711,9 @@
   </si>
   <si>
     <t>Note that internal business rules will determine the appropriate transitions that may occur between statuses (and also classes).</t>
+  </si>
+  <si>
+    <t>in-progress</t>
   </si>
   <si>
     <t>Current state of the encounter.</t>
@@ -4304,7 +4307,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>220</v>
       </c>
@@ -4320,7 +4323,7 @@
         <v>82</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>83</v>
@@ -4349,7 +4352,7 @@
         <v>76</v>
       </c>
       <c r="R22" t="s" s="2">
-        <v>76</v>
+        <v>224</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>76</v>
@@ -4367,10 +4370,10 @@
         <v>172</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>76</v>
@@ -4403,21 +4406,21 @@
         <v>94</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -4440,16 +4443,16 @@
         <v>76</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
@@ -4499,7 +4502,7 @@
         <v>76</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>74</v>
@@ -4528,7 +4531,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -4637,7 +4640,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -4748,11 +4751,11 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -4774,10 +4777,10 @@
         <v>127</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>145</v>
@@ -4832,7 +4835,7 @@
         <v>76</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>74</v>
@@ -4861,7 +4864,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -4920,10 +4923,10 @@
         <v>172</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>76</v>
@@ -4941,7 +4944,7 @@
         <v>76</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>82</v>
@@ -4970,7 +4973,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4996,10 +4999,10 @@
         <v>206</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -5050,7 +5053,7 @@
         <v>76</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>82</v>
@@ -5079,7 +5082,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5102,13 +5105,13 @@
         <v>83</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
@@ -5138,10 +5141,10 @@
         <v>183</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>76</v>
@@ -5159,7 +5162,7 @@
         <v>76</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>82</v>
@@ -5177,18 +5180,18 @@
         <v>76</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5211,13 +5214,13 @@
         <v>76</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -5268,7 +5271,7 @@
         <v>76</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>74</v>
@@ -5297,7 +5300,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5406,7 +5409,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -5517,11 +5520,11 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -5543,10 +5546,10 @@
         <v>127</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M33" t="s" s="2">
         <v>145</v>
@@ -5601,7 +5604,7 @@
         <v>76</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>74</v>
@@ -5630,7 +5633,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5653,13 +5656,13 @@
         <v>76</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -5689,10 +5692,10 @@
         <v>183</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>76</v>
@@ -5710,7 +5713,7 @@
         <v>76</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>82</v>
@@ -5739,7 +5742,7 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5765,10 +5768,10 @@
         <v>206</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -5819,7 +5822,7 @@
         <v>76</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>82</v>
@@ -5848,7 +5851,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -5874,13 +5877,13 @@
         <v>178</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
@@ -5906,13 +5909,13 @@
         <v>76</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Z36" t="s" s="2">
         <v>76</v>
@@ -5930,7 +5933,7 @@
         <v>76</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>74</v>
@@ -5945,21 +5948,21 @@
         <v>94</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -5985,10 +5988,10 @@
         <v>178</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
@@ -6015,13 +6018,13 @@
         <v>76</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z37" t="s" s="2">
         <v>76</v>
@@ -6039,7 +6042,7 @@
         <v>76</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>74</v>
@@ -6054,7 +6057,7 @@
         <v>94</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>161</v>
@@ -6063,12 +6066,12 @@
         <v>76</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6094,10 +6097,10 @@
         <v>178</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -6124,13 +6127,13 @@
         <v>76</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Z38" t="s" s="2">
         <v>76</v>
@@ -6148,7 +6151,7 @@
         <v>76</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>74</v>
@@ -6166,22 +6169,22 @@
         <v>76</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6200,16 +6203,16 @@
         <v>83</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
@@ -6259,7 +6262,7 @@
         <v>76</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>74</v>
@@ -6274,21 +6277,21 @@
         <v>94</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6311,13 +6314,13 @@
         <v>83</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -6368,7 +6371,7 @@
         <v>76</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>74</v>
@@ -6383,25 +6386,25 @@
         <v>94</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>161</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -6420,13 +6423,13 @@
         <v>76</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -6477,7 +6480,7 @@
         <v>76</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>74</v>
@@ -6492,10 +6495,10 @@
         <v>94</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>76</v>
@@ -6506,7 +6509,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6529,13 +6532,13 @@
         <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
@@ -6586,7 +6589,7 @@
         <v>76</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>74</v>
@@ -6601,21 +6604,21 @@
         <v>94</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -6724,7 +6727,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -6835,11 +6838,11 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -6861,10 +6864,10 @@
         <v>127</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M45" t="s" s="2">
         <v>145</v>
@@ -6919,7 +6922,7 @@
         <v>76</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>74</v>
@@ -6948,7 +6951,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -6974,13 +6977,13 @@
         <v>178</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
@@ -7009,10 +7012,10 @@
         <v>183</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z46" t="s" s="2">
         <v>76</v>
@@ -7030,7 +7033,7 @@
         <v>76</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>74</v>
@@ -7045,21 +7048,21 @@
         <v>94</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -7085,10 +7088,10 @@
         <v>206</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -7139,7 +7142,7 @@
         <v>76</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>74</v>
@@ -7157,18 +7160,18 @@
         <v>76</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -7191,13 +7194,13 @@
         <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7248,7 +7251,7 @@
         <v>76</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>74</v>
@@ -7263,21 +7266,21 @@
         <v>94</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -7300,13 +7303,13 @@
         <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
@@ -7357,7 +7360,7 @@
         <v>76</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>74</v>
@@ -7372,21 +7375,21 @@
         <v>94</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
@@ -7412,13 +7415,13 @@
         <v>206</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
@@ -7468,7 +7471,7 @@
         <v>76</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>74</v>
@@ -7483,21 +7486,21 @@
         <v>94</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -7520,16 +7523,16 @@
         <v>76</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
@@ -7579,7 +7582,7 @@
         <v>76</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>74</v>
@@ -7594,25 +7597,25 @@
         <v>94</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7634,13 +7637,13 @@
         <v>178</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
@@ -7669,10 +7672,10 @@
         <v>106</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z52" t="s" s="2">
         <v>76</v>
@@ -7690,7 +7693,7 @@
         <v>76</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>74</v>
@@ -7705,25 +7708,25 @@
         <v>94</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -7742,16 +7745,16 @@
         <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
@@ -7801,7 +7804,7 @@
         <v>76</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>74</v>
@@ -7816,21 +7819,21 @@
         <v>94</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -7853,13 +7856,13 @@
         <v>83</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
@@ -7910,7 +7913,7 @@
         <v>76</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>74</v>
@@ -7928,7 +7931,7 @@
         <v>76</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>76</v>
@@ -7939,7 +7942,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
@@ -8048,7 +8051,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8159,11 +8162,11 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8185,10 +8188,10 @@
         <v>127</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M57" t="s" s="2">
         <v>145</v>
@@ -8243,7 +8246,7 @@
         <v>76</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>74</v>
@@ -8272,11 +8275,11 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -8295,16 +8298,16 @@
         <v>83</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
@@ -8354,7 +8357,7 @@
         <v>76</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>82</v>
@@ -8369,21 +8372,21 @@
         <v>94</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8409,10 +8412,10 @@
         <v>178</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -8442,10 +8445,10 @@
         <v>106</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Z59" t="s" s="2">
         <v>76</v>
@@ -8463,7 +8466,7 @@
         <v>76</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>74</v>
@@ -8492,7 +8495,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -8515,13 +8518,13 @@
         <v>76</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -8572,7 +8575,7 @@
         <v>76</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>74</v>
@@ -8590,7 +8593,7 @@
         <v>76</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>76</v>
@@ -8601,7 +8604,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -8624,16 +8627,16 @@
         <v>76</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
@@ -8683,7 +8686,7 @@
         <v>76</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>74</v>
@@ -8701,7 +8704,7 @@
         <v>76</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>76</v>
@@ -8712,7 +8715,7 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -8735,16 +8738,16 @@
         <v>76</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
@@ -8794,7 +8797,7 @@
         <v>76</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>74</v>
@@ -8812,7 +8815,7 @@
         <v>76</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>76</v>
@@ -8823,7 +8826,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -8932,7 +8935,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9043,11 +9046,11 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9069,10 +9072,10 @@
         <v>127</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>145</v>
@@ -9127,7 +9130,7 @@
         <v>76</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>74</v>
@@ -9156,7 +9159,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9182,10 +9185,10 @@
         <v>149</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -9236,7 +9239,7 @@
         <v>76</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>74</v>
@@ -9260,12 +9263,12 @@
         <v>76</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
@@ -9288,13 +9291,13 @@
         <v>76</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -9345,7 +9348,7 @@
         <v>76</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>74</v>
@@ -9363,7 +9366,7 @@
         <v>76</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>76</v>
@@ -9374,7 +9377,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
@@ -9400,10 +9403,10 @@
         <v>178</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -9433,10 +9436,10 @@
         <v>106</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z68" t="s" s="2">
         <v>76</v>
@@ -9454,7 +9457,7 @@
         <v>76</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>74</v>
@@ -9472,18 +9475,18 @@
         <v>76</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
@@ -9509,10 +9512,10 @@
         <v>178</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -9539,13 +9542,13 @@
         <v>76</v>
       </c>
       <c r="W69" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Z69" t="s" s="2">
         <v>76</v>
@@ -9563,7 +9566,7 @@
         <v>76</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>74</v>
@@ -9587,12 +9590,12 @@
         <v>76</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
@@ -9618,16 +9621,16 @@
         <v>178</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O70" t="s" s="2">
         <v>76</v>
@@ -9652,13 +9655,13 @@
         <v>76</v>
       </c>
       <c r="W70" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>76</v>
@@ -9676,7 +9679,7 @@
         <v>76</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>74</v>
@@ -9694,18 +9697,18 @@
         <v>76</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
@@ -9731,10 +9734,10 @@
         <v>178</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
@@ -9764,10 +9767,10 @@
         <v>106</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>76</v>
@@ -9785,7 +9788,7 @@
         <v>76</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>74</v>
@@ -9803,18 +9806,18 @@
         <v>76</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -9840,10 +9843,10 @@
         <v>178</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
@@ -9873,10 +9876,10 @@
         <v>106</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z72" t="s" s="2">
         <v>76</v>
@@ -9894,7 +9897,7 @@
         <v>76</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>74</v>
@@ -9912,18 +9915,18 @@
         <v>76</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -9946,13 +9949,13 @@
         <v>76</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
@@ -10003,7 +10006,7 @@
         <v>76</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>74</v>
@@ -10021,18 +10024,18 @@
         <v>76</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
@@ -10058,10 +10061,10 @@
         <v>178</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -10088,13 +10091,13 @@
         <v>76</v>
       </c>
       <c r="W74" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Z74" t="s" s="2">
         <v>76</v>
@@ -10112,7 +10115,7 @@
         <v>76</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>74</v>
@@ -10130,18 +10133,18 @@
         <v>76</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
@@ -10164,16 +10167,16 @@
         <v>76</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
@@ -10223,7 +10226,7 @@
         <v>76</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>74</v>
@@ -10241,7 +10244,7 @@
         <v>76</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>76</v>
@@ -10252,7 +10255,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
@@ -10361,7 +10364,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
@@ -10472,11 +10475,11 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10498,10 +10501,10 @@
         <v>127</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M78" t="s" s="2">
         <v>145</v>
@@ -10556,7 +10559,7 @@
         <v>76</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>74</v>
@@ -10585,7 +10588,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
@@ -10608,13 +10611,13 @@
         <v>76</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
@@ -10665,7 +10668,7 @@
         <v>76</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>82</v>
@@ -10680,21 +10683,21 @@
         <v>94</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
@@ -10720,13 +10723,13 @@
         <v>102</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
@@ -10755,10 +10758,10 @@
         <v>172</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z80" t="s" s="2">
         <v>76</v>
@@ -10776,7 +10779,7 @@
         <v>76</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>74</v>
@@ -10794,7 +10797,7 @@
         <v>76</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>76</v>
@@ -10805,7 +10808,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
@@ -10831,13 +10834,13 @@
         <v>178</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
@@ -10863,13 +10866,13 @@
         <v>76</v>
       </c>
       <c r="W81" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="Z81" t="s" s="2">
         <v>76</v>
@@ -10887,7 +10890,7 @@
         <v>76</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>74</v>
@@ -10916,7 +10919,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
@@ -10942,10 +10945,10 @@
         <v>206</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
@@ -10996,7 +10999,7 @@
         <v>76</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>74</v>
@@ -11014,7 +11017,7 @@
         <v>76</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>76</v>
@@ -11025,7 +11028,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
@@ -11051,10 +11054,10 @@
         <v>213</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
@@ -11105,7 +11108,7 @@
         <v>76</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>74</v>
@@ -11120,21 +11123,21 @@
         <v>94</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
@@ -11157,16 +11160,16 @@
         <v>76</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
@@ -11216,7 +11219,7 @@
         <v>76</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>74</v>
@@ -11231,10 +11234,10 @@
         <v>94</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>76</v>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T15:14:06+00:00</t>
+    <t>2023-01-25T17:01:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
     <t>Note that internal business rules will determine the appropriate transitions that may occur between statuses (and also classes).</t>
   </si>
   <si>
-    <t>in-progress</t>
+    <t>finished</t>
   </si>
   <si>
     <t>Current state of the encounter.</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T17:01:00+00:00</t>
+    <t>2023-01-27T16:08:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T16:08:13+00:00</t>
+    <t>2023-01-27T21:59:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T21:59:50+00:00</t>
+    <t>2023-01-27T22:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T22:08:27+00:00</t>
+    <t>2023-01-31T04:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:34:49+00:00</t>
+    <t>2023-01-31T04:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:42:38+00:00</t>
+    <t>2023-01-31T18:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T12:10:18+00:00</t>
+    <t>2023-02-07T22:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T22:15:28+00:00</t>
+    <t>2023-02-08T07:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-08T07:55:54+00:00</t>
+    <t>2023-02-09T15:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T15:16:32+00:00</t>
+    <t>2023-02-09T17:43:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T17:43:27+00:00</t>
+    <t>2023-02-09T21:16:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T21:16:20+00:00</t>
+    <t>2023-02-10T06:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T06:44:21+00:00</t>
+    <t>2023-02-10T12:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T12:56:00+00:00</t>
+    <t>2023-02-10T14:37:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T14:37:40+00:00</t>
+    <t>2023-02-10T15:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T15:20:03+00:00</t>
+    <t>2023-02-10T23:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T23:42:05+00:00</t>
+    <t>2023-02-13T12:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T12:09:55+00:00</t>
+    <t>2023-02-13T14:15:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:15:11+00:00</t>
+    <t>2023-02-13T14:19:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:19:18+00:00</t>
+    <t>2023-02-13T18:35:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:35:48+00:00</t>
+    <t>2023-02-13T18:37:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:37:08+00:00</t>
+    <t>2023-02-13T18:51:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:51:39+00:00</t>
+    <t>2023-02-13T20:10:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T20:10:13+00:00</t>
+    <t>2023-02-14T12:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T12:04:08+00:00</t>
+    <t>2023-02-14T14:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:41:39+00:00</t>
+    <t>2023-02-14T14:58:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:58:50+00:00</t>
+    <t>2023-02-14T15:00:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T15:00:34+00:00</t>
+    <t>2023-02-14T18:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T18:30:52+00:00</t>
+    <t>2023-02-14T21:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T21:42:45+00:00</t>
+    <t>2023-02-15T05:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T05:04:04+00:00</t>
+    <t>2023-02-15T13:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T13:37:26+00:00</t>
+    <t>2023-02-15T14:04:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T14:04:38+00:00</t>
+    <t>2023-02-15T16:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:11:45+00:00</t>
+    <t>2023-02-15T16:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:17:51+00:00</t>
+    <t>2023-02-15T16:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:20:01+00:00</t>
+    <t>2023-02-15T16:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:22:21+00:00</t>
+    <t>2023-02-15T20:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T20:04:03+00:00</t>
+    <t>2023-02-16T23:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-16T23:28:10+00:00</t>
+    <t>2023-02-17T19:45:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-17T19:45:07+00:00</t>
+    <t>2023-02-20T03:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:17:07+00:00</t>
+    <t>2023-02-20T03:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:26:30+00:00</t>
+    <t>2023-02-20T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T15:31:02+00:00</t>
+    <t>2023-02-20T22:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T22:25:44+00:00</t>
+    <t>2023-02-21T14:23:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T14:23:26+00:00</t>
+    <t>2023-02-21T19:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T19:28:17+00:00</t>
+    <t>2023-02-22T15:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T15:40:59+00:00</t>
+    <t>2023-02-22T16:44:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T16:44:04+00:00</t>
+    <t>2023-02-22T20:35:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T20:35:25+00:00</t>
+    <t>2023-02-27T14:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T14:20:24+00:00</t>
+    <t>2023-02-27T15:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$82</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2949" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2881" uniqueCount="512">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T15:22:20+00:00</t>
+    <t>2023-03-02T15:13:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -412,131 +412,104 @@
     <t>Encounter.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Encounter.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Encounter.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Identifier(s) by which this encounter is known</t>
+  </si>
+  <si>
+    <t>Identifier(s) by which this encounter is known.</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>PV1-19</t>
+  </si>
+  <si>
+    <t>Encounter.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Encounter.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>open</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>PertinenciaAtencionBox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ExtBoolPertinenciaAtencionBox}
-</t>
-  </si>
-  <si>
-    <t>ExtBool Pertinencia Atencion Box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>MotivoNoPertinencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ExtStringMotivoNoPertinencia}
-</t>
-  </si>
-  <si>
-    <t>ExtString MotivoNoPertinencia</t>
-  </si>
-  <si>
-    <t>Encounter.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Encounter.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Identifier(s) by which this encounter is known</t>
-  </si>
-  <si>
-    <t>Identifier(s) by which this encounter is known.</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>PV1-19</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -1933,11 +1906,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM84"/>
+  <dimension ref="A1:AM82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.67578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="22.87890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="12.66015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2875,11 +2848,11 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>76</v>
@@ -2894,15 +2867,17 @@
         <v>77</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="M9" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="N9" s="2"/>
       <c r="O9" t="s" s="2">
         <v>77</v>
@@ -2939,14 +2914,16 @@
         <v>77</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AB9" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AC9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
         <v>133</v>
@@ -2967,7 +2944,7 @@
         <v>77</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>77</v>
@@ -2976,43 +2953,45 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="B10" t="s" s="2">
         <v>135</v>
       </c>
+      <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H10" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H10" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="I10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J10" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="K10" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="K10" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+      <c r="M10" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O10" t="s" s="2">
         <v>77</v>
       </c>
@@ -3060,7 +3039,7 @@
         <v>77</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="AF10" t="s" s="2">
         <v>75</v>
@@ -3069,7 +3048,7 @@
         <v>76</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>134</v>
@@ -3078,7 +3057,7 @@
         <v>77</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>77</v>
@@ -3089,17 +3068,15 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>83</v>
@@ -3111,16 +3088,16 @@
         <v>77</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -3171,7 +3148,7 @@
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>75</v>
@@ -3180,63 +3157,59 @@
         <v>76</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>77</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
         <v>77</v>
       </c>
@@ -3284,25 +3257,25 @@
         <v>77</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>77</v>
@@ -3311,40 +3284,42 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="M13" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
         <v>77</v>
@@ -3381,19 +3356,19 @@
         <v>77</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="AC13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>75</v>
@@ -3405,24 +3380,24 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AK13" t="s" s="2">
-        <v>154</v>
-      </c>
       <c r="AL13" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -3439,22 +3414,26 @@
         <v>77</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>158</v>
+        <v>103</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O14" t="s" s="2">
         <v>77</v>
       </c>
@@ -3478,13 +3457,13 @@
         <v>77</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="Z14" t="s" s="2">
         <v>77</v>
@@ -3502,7 +3481,7 @@
         <v>77</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>75</v>
@@ -3514,35 +3493,35 @@
         <v>77</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>77</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>77</v>
@@ -3551,21 +3530,23 @@
         <v>77</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>128</v>
+        <v>171</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O15" t="s" s="2">
         <v>77</v>
       </c>
@@ -3589,60 +3570,60 @@
         <v>77</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="Z15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AC15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -3659,25 +3640,25 @@
         <v>77</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>77</v>
@@ -3690,7 +3671,7 @@
         <v>77</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>77</v>
@@ -3702,13 +3683,13 @@
         <v>77</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>174</v>
+        <v>77</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="Z16" t="s" s="2">
         <v>77</v>
@@ -3726,7 +3707,7 @@
         <v>77</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>75</v>
@@ -3744,18 +3725,18 @@
         <v>77</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>126</v>
+        <v>189</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -3763,13 +3744,13 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3778,20 +3759,18 @@
         <v>84</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
         <v>77</v>
       </c>
@@ -3803,7 +3782,7 @@
         <v>77</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>77</v>
@@ -3815,13 +3794,13 @@
         <v>77</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>186</v>
+        <v>77</v>
       </c>
       <c r="Z17" t="s" s="2">
         <v>77</v>
@@ -3839,7 +3818,7 @@
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>75</v>
@@ -3857,18 +3836,18 @@
         <v>77</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>188</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -3891,20 +3870,16 @@
         <v>84</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>97</v>
+        <v>199</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
         <v>77</v>
       </c>
@@ -3916,7 +3891,7 @@
         <v>77</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>77</v>
@@ -3952,7 +3927,7 @@
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>75</v>
@@ -3970,18 +3945,18 @@
         <v>77</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -3989,13 +3964,13 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
@@ -4004,16 +3979,16 @@
         <v>84</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
@@ -4027,7 +4002,7 @@
         <v>77</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>77</v>
@@ -4063,7 +4038,7 @@
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>75</v>
@@ -4081,18 +4056,18 @@
         <v>77</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -4100,30 +4075,32 @@
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>207</v>
+        <v>103</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="M20" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
         <v>77</v>
@@ -4133,7 +4110,7 @@
         <v>77</v>
       </c>
       <c r="R20" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>77</v>
@@ -4148,13 +4125,13 @@
         <v>77</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>77</v>
+        <v>219</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>77</v>
@@ -4172,10 +4149,10 @@
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>83</v>
@@ -4187,21 +4164,21 @@
         <v>95</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>77</v>
+        <v>222</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>212</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -4212,7 +4189,7 @@
         <v>75</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>77</v>
@@ -4221,19 +4198,19 @@
         <v>77</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
@@ -4283,13 +4260,13 @@
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>77</v>
@@ -4301,18 +4278,18 @@
         <v>77</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>219</v>
+        <v>153</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>220</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -4320,32 +4297,30 @@
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>222</v>
+        <v>150</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
         <v>77</v>
@@ -4355,7 +4330,7 @@
         <v>77</v>
       </c>
       <c r="R22" t="s" s="2">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>77</v>
@@ -4370,13 +4345,13 @@
         <v>77</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>226</v>
+        <v>77</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>227</v>
+        <v>77</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>77</v>
@@ -4394,10 +4369,10 @@
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>221</v>
+        <v>152</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -4406,28 +4381,28 @@
         <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>229</v>
+        <v>153</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>230</v>
+        <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>231</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
@@ -4446,16 +4421,16 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>233</v>
+        <v>129</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>234</v>
+        <v>130</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>155</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>132</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
@@ -4505,7 +4480,7 @@
         <v>77</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>232</v>
+        <v>159</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>75</v>
@@ -4517,13 +4492,13 @@
         <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>77</v>
@@ -4534,39 +4509,43 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>159</v>
+        <v>233</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4614,25 +4593,25 @@
         <v>77</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>77</v>
@@ -4643,18 +4622,18 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>77</v>
@@ -4666,17 +4645,15 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="M25" s="2"/>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
         <v>77</v>
@@ -4701,13 +4678,13 @@
         <v>77</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>77</v>
+        <v>219</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>77</v>
@@ -4725,25 +4702,25 @@
         <v>77</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>167</v>
+        <v>236</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>77</v>
@@ -4754,43 +4731,39 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>240</v>
+        <v>77</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>128</v>
+        <v>199</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4838,25 +4811,25 @@
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>77</v>
@@ -4867,7 +4840,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -4887,16 +4860,16 @@
         <v>77</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>103</v>
+        <v>241</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -4923,13 +4896,13 @@
         <v>77</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>77</v>
@@ -4947,7 +4920,7 @@
         <v>77</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>83</v>
@@ -4965,18 +4938,18 @@
         <v>77</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>162</v>
+        <v>246</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>77</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4984,10 +4957,10 @@
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>77</v>
@@ -4999,13 +4972,13 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -5056,13 +5029,13 @@
         <v>77</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>77</v>
@@ -5074,7 +5047,7 @@
         <v>77</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>77</v>
@@ -5085,7 +5058,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5093,7 +5066,7 @@
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>83</v>
@@ -5105,16 +5078,16 @@
         <v>77</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>249</v>
+        <v>149</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>251</v>
+        <v>151</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
@@ -5141,13 +5114,13 @@
         <v>77</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>252</v>
+        <v>77</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>253</v>
+        <v>77</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>77</v>
@@ -5165,10 +5138,10 @@
         <v>77</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>248</v>
+        <v>152</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -5177,28 +5150,28 @@
         <v>77</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>254</v>
+        <v>153</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>255</v>
+        <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>256</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -5217,15 +5190,17 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>233</v>
+        <v>129</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>258</v>
+        <v>130</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="M30" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
         <v>77</v>
@@ -5274,7 +5249,7 @@
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>257</v>
+        <v>159</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>75</v>
@@ -5286,13 +5261,13 @@
         <v>77</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>77</v>
@@ -5303,39 +5278,43 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>159</v>
+        <v>233</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5383,25 +5362,25 @@
         <v>77</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>77</v>
@@ -5412,18 +5391,18 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>77</v>
@@ -5435,17 +5414,15 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>128</v>
+        <v>241</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
         <v>77</v>
@@ -5470,13 +5447,13 @@
         <v>77</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>77</v>
+        <v>245</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>77</v>
@@ -5494,25 +5471,25 @@
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>167</v>
+        <v>255</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>77</v>
@@ -5523,43 +5500,39 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>240</v>
+        <v>77</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>128</v>
+        <v>199</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5607,25 +5580,25 @@
         <v>77</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>77</v>
@@ -5636,7 +5609,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5644,10 +5617,10 @@
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>77</v>
@@ -5656,18 +5629,20 @@
         <v>77</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>249</v>
+        <v>171</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L34" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
         <v>77</v>
@@ -5692,13 +5667,13 @@
         <v>77</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>184</v>
+        <v>265</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>77</v>
@@ -5716,13 +5691,13 @@
         <v>77</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>77</v>
@@ -5731,21 +5706,21 @@
         <v>95</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>77</v>
+        <v>268</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>162</v>
+        <v>269</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>77</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5753,7 +5728,7 @@
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>83</v>
@@ -5765,16 +5740,16 @@
         <v>77</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>207</v>
+        <v>171</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -5801,13 +5776,13 @@
         <v>77</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>77</v>
+        <v>265</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>77</v>
@@ -5825,10 +5800,10 @@
         <v>77</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -5840,21 +5815,21 @@
         <v>95</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>77</v>
+        <v>268</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -5865,7 +5840,7 @@
         <v>75</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>77</v>
@@ -5874,20 +5849,18 @@
         <v>77</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
         <v>77</v>
@@ -5912,13 +5885,13 @@
         <v>77</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Z36" t="s" s="2">
         <v>77</v>
@@ -5936,13 +5909,13 @@
         <v>77</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>77</v>
@@ -5951,25 +5924,25 @@
         <v>95</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>276</v>
+        <v>77</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
-        <v>77</v>
+        <v>285</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -5988,15 +5961,17 @@
         <v>84</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>179</v>
+        <v>286</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="M37" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
         <v>77</v>
@@ -6021,13 +5996,13 @@
         <v>77</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>283</v>
+        <v>77</v>
       </c>
       <c r="Z37" t="s" s="2">
         <v>77</v>
@@ -6045,7 +6020,7 @@
         <v>77</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>75</v>
@@ -6060,21 +6035,21 @@
         <v>95</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>162</v>
+        <v>291</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>77</v>
+        <v>292</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6085,7 +6060,7 @@
         <v>75</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>77</v>
@@ -6094,16 +6069,16 @@
         <v>77</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>179</v>
+        <v>295</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -6130,13 +6105,13 @@
         <v>77</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>287</v>
+        <v>77</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>288</v>
+        <v>77</v>
       </c>
       <c r="Z38" t="s" s="2">
         <v>77</v>
@@ -6154,13 +6129,13 @@
         <v>77</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>77</v>
@@ -6169,32 +6144,32 @@
         <v>95</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>289</v>
+        <v>153</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F39" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>77</v>
@@ -6203,20 +6178,18 @@
         <v>77</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
         <v>77</v>
@@ -6265,13 +6238,13 @@
         <v>77</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>77</v>
@@ -6280,21 +6253,21 @@
         <v>95</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>301</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6317,13 +6290,13 @@
         <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>303</v>
+        <v>225</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -6374,7 +6347,7 @@
         <v>77</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>75</v>
@@ -6389,35 +6362,35 @@
         <v>95</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>162</v>
+        <v>312</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>307</v>
+        <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>310</v>
+        <v>77</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6426,13 +6399,13 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>311</v>
+        <v>149</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>312</v>
+        <v>150</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>313</v>
+        <v>151</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -6483,25 +6456,25 @@
         <v>77</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>309</v>
+        <v>152</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>314</v>
+        <v>77</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>315</v>
+        <v>153</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>77</v>
@@ -6512,11 +6485,11 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6532,18 +6505,20 @@
         <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>233</v>
+        <v>129</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>317</v>
+        <v>130</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="M42" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
         <v>77</v>
@@ -6592,7 +6567,7 @@
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>316</v>
+        <v>159</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>75</v>
@@ -6604,56 +6579,60 @@
         <v>77</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>319</v>
+        <v>77</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>320</v>
+        <v>153</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>321</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F43" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>159</v>
+        <v>233</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="M43" s="2"/>
-      <c r="N43" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6701,25 +6680,25 @@
         <v>77</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>77</v>
@@ -6730,11 +6709,11 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -6750,19 +6729,19 @@
         <v>77</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>128</v>
+        <v>171</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>164</v>
+        <v>318</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>165</v>
+        <v>319</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>146</v>
+        <v>320</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
@@ -6788,13 +6767,13 @@
         <v>77</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>77</v>
+        <v>319</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>77</v>
+        <v>321</v>
       </c>
       <c r="Z44" t="s" s="2">
         <v>77</v>
@@ -6812,7 +6791,7 @@
         <v>77</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>167</v>
+        <v>317</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>75</v>
@@ -6824,60 +6803,56 @@
         <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>77</v>
+        <v>322</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>162</v>
+        <v>323</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>77</v>
+        <v>324</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
-        <v>240</v>
+        <v>77</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>128</v>
+        <v>199</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>241</v>
+        <v>326</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
         <v>77</v>
       </c>
@@ -6925,36 +6900,36 @@
         <v>77</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>243</v>
+        <v>325</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>126</v>
+        <v>328</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>77</v>
+        <v>329</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -6965,7 +6940,7 @@
         <v>75</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>77</v>
@@ -6977,17 +6952,15 @@
         <v>84</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>179</v>
+        <v>331</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
         <v>77</v>
@@ -7012,13 +6985,13 @@
         <v>77</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>329</v>
+        <v>77</v>
       </c>
       <c r="Z46" t="s" s="2">
         <v>77</v>
@@ -7036,13 +7009,13 @@
         <v>77</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>77</v>
@@ -7051,21 +7024,21 @@
         <v>95</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>77</v>
+        <v>336</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -7076,7 +7049,7 @@
         <v>75</v>
       </c>
       <c r="F47" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>77</v>
@@ -7085,16 +7058,16 @@
         <v>77</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>207</v>
+        <v>339</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -7145,13 +7118,13 @@
         <v>77</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>77</v>
@@ -7160,21 +7133,21 @@
         <v>95</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -7194,18 +7167,20 @@
         <v>77</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>339</v>
+        <v>199</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="M48" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
         <v>77</v>
@@ -7254,7 +7229,7 @@
         <v>77</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>75</v>
@@ -7269,21 +7244,21 @@
         <v>95</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -7294,7 +7269,7 @@
         <v>75</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>77</v>
@@ -7303,18 +7278,20 @@
         <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="M49" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
         <v>77</v>
@@ -7363,13 +7340,13 @@
         <v>77</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>77</v>
@@ -7378,32 +7355,32 @@
         <v>95</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F50" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>77</v>
@@ -7412,19 +7389,19 @@
         <v>77</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>207</v>
+        <v>171</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
@@ -7450,13 +7427,13 @@
         <v>77</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>77</v>
+        <v>364</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>77</v>
+        <v>365</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>77</v>
@@ -7474,13 +7451,13 @@
         <v>77</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>77</v>
@@ -7489,32 +7466,32 @@
         <v>95</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>359</v>
+        <v>369</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F51" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>77</v>
@@ -7523,19 +7500,19 @@
         <v>77</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
@@ -7585,13 +7562,13 @@
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>77</v>
@@ -7600,25 +7577,25 @@
         <v>95</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7637,17 +7614,15 @@
         <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>179</v>
+        <v>225</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="M52" s="2"/>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
         <v>77</v>
@@ -7672,31 +7647,31 @@
         <v>77</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>372</v>
+        <v>77</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE52" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>75</v>
@@ -7711,32 +7686,32 @@
         <v>95</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>374</v>
+        <v>77</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>376</v>
+        <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>377</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F53" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>77</v>
@@ -7745,20 +7720,18 @@
         <v>77</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>379</v>
+        <v>149</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>380</v>
+        <v>150</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
         <v>77</v>
@@ -7807,40 +7780,40 @@
         <v>77</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>378</v>
+        <v>152</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>374</v>
+        <v>77</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>375</v>
+        <v>153</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>376</v>
+        <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>377</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -7856,18 +7829,20 @@
         <v>77</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>233</v>
+        <v>129</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>382</v>
+        <v>130</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="M54" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
         <v>77</v>
@@ -7916,7 +7891,7 @@
         <v>77</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>381</v>
+        <v>159</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>75</v>
@@ -7928,13 +7903,13 @@
         <v>77</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>384</v>
+        <v>153</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>77</v>
@@ -7945,39 +7920,43 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>159</v>
+        <v>233</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="M55" s="2"/>
-      <c r="N55" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O55" t="s" s="2">
         <v>77</v>
       </c>
@@ -8025,25 +8004,25 @@
         <v>77</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>77</v>
@@ -8054,18 +8033,18 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
-        <v>143</v>
+        <v>381</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>77</v>
@@ -8074,19 +8053,19 @@
         <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>128</v>
+        <v>382</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>164</v>
+        <v>383</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>165</v>
+        <v>384</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>146</v>
+        <v>363</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
@@ -8136,72 +8115,68 @@
         <v>77</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>167</v>
+        <v>380</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>77</v>
+        <v>385</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>162</v>
+        <v>386</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>77</v>
+        <v>387</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>240</v>
+        <v>77</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>128</v>
+        <v>171</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>241</v>
+        <v>389</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8225,13 +8200,13 @@
         <v>77</v>
       </c>
       <c r="W57" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>77</v>
+        <v>391</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>77</v>
+        <v>392</v>
       </c>
       <c r="Z57" t="s" s="2">
         <v>77</v>
@@ -8249,25 +8224,25 @@
         <v>77</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>243</v>
+        <v>388</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>77</v>
@@ -8278,15 +8253,15 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>389</v>
+        <v>77</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>83</v>
@@ -8298,20 +8273,18 @@
         <v>77</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="M58" s="2"/>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
         <v>77</v>
@@ -8360,10 +8333,10 @@
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -8375,21 +8348,21 @@
         <v>95</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>393</v>
+        <v>77</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>376</v>
+        <v>77</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>395</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8400,7 +8373,7 @@
         <v>75</v>
       </c>
       <c r="F59" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>77</v>
@@ -8412,15 +8385,17 @@
         <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>179</v>
+        <v>399</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="M59" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
         <v>77</v>
@@ -8445,13 +8420,13 @@
         <v>77</v>
       </c>
       <c r="W59" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>399</v>
+        <v>77</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>400</v>
+        <v>77</v>
       </c>
       <c r="Z59" t="s" s="2">
         <v>77</v>
@@ -8469,13 +8444,13 @@
         <v>77</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>77</v>
@@ -8487,7 +8462,7 @@
         <v>77</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>162</v>
+        <v>403</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>77</v>
@@ -8498,7 +8473,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -8521,15 +8496,17 @@
         <v>77</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>402</v>
+        <v>225</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="M60" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
         <v>77</v>
@@ -8578,7 +8555,7 @@
         <v>77</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>75</v>
@@ -8596,7 +8573,7 @@
         <v>77</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>77</v>
@@ -8607,7 +8584,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -8618,7 +8595,7 @@
         <v>75</v>
       </c>
       <c r="F61" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>77</v>
@@ -8630,17 +8607,15 @@
         <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>407</v>
+        <v>149</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>408</v>
+        <v>150</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="M61" s="2"/>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
         <v>77</v>
@@ -8689,25 +8664,25 @@
         <v>77</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>406</v>
+        <v>152</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>411</v>
+        <v>153</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>77</v>
@@ -8718,18 +8693,18 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F62" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>77</v>
@@ -8741,16 +8716,16 @@
         <v>77</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>233</v>
+        <v>129</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>413</v>
+        <v>130</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>414</v>
+        <v>155</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>415</v>
+        <v>132</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
@@ -8800,25 +8775,25 @@
         <v>77</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>412</v>
+        <v>159</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>416</v>
+        <v>153</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>77</v>
@@ -8829,39 +8804,43 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F63" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>159</v>
+        <v>233</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O63" t="s" s="2">
         <v>77</v>
       </c>
@@ -8909,25 +8888,25 @@
         <v>77</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>77</v>
@@ -8938,18 +8917,18 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F64" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>77</v>
@@ -8961,17 +8940,15 @@
         <v>77</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>164</v>
+        <v>413</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
         <v>77</v>
@@ -9020,72 +8997,68 @@
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>167</v>
+        <v>412</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>77</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
-        <v>240</v>
+        <v>77</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F65" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>128</v>
+        <v>417</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>241</v>
+        <v>418</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
         <v>77</v>
       </c>
@@ -9133,25 +9106,25 @@
         <v>77</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>243</v>
+        <v>416</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>126</v>
+        <v>420</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>77</v>
@@ -9162,7 +9135,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9185,13 +9158,13 @@
         <v>77</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -9218,13 +9191,13 @@
         <v>77</v>
       </c>
       <c r="W66" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>77</v>
+        <v>424</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>77</v>
+        <v>425</v>
       </c>
       <c r="Z66" t="s" s="2">
         <v>77</v>
@@ -9242,7 +9215,7 @@
         <v>77</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>75</v>
@@ -9260,18 +9233,18 @@
         <v>77</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>154</v>
+        <v>426</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
@@ -9294,13 +9267,13 @@
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>425</v>
+        <v>171</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -9327,13 +9300,13 @@
         <v>77</v>
       </c>
       <c r="W67" t="s" s="2">
-        <v>77</v>
+        <v>265</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>77</v>
+        <v>431</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>77</v>
+        <v>432</v>
       </c>
       <c r="Z67" t="s" s="2">
         <v>77</v>
@@ -9351,7 +9324,7 @@
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>75</v>
@@ -9369,18 +9342,18 @@
         <v>77</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>428</v>
+        <v>153</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>77</v>
+        <v>433</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
@@ -9391,7 +9364,7 @@
         <v>75</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>77</v>
@@ -9403,16 +9376,20 @@
         <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="O68" t="s" s="2">
         <v>77</v>
       </c>
@@ -9436,13 +9413,13 @@
         <v>77</v>
       </c>
       <c r="W68" t="s" s="2">
-        <v>107</v>
+        <v>265</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="Z68" t="s" s="2">
         <v>77</v>
@@ -9460,13 +9437,13 @@
         <v>77</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>77</v>
@@ -9478,18 +9455,18 @@
         <v>77</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
@@ -9500,7 +9477,7 @@
         <v>75</v>
       </c>
       <c r="F69" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>77</v>
@@ -9512,13 +9489,13 @@
         <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -9545,13 +9522,13 @@
         <v>77</v>
       </c>
       <c r="W69" t="s" s="2">
-        <v>273</v>
+        <v>107</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="Z69" t="s" s="2">
         <v>77</v>
@@ -9569,13 +9546,13 @@
         <v>77</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>77</v>
@@ -9587,18 +9564,18 @@
         <v>77</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>162</v>
+        <v>448</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
@@ -9621,20 +9598,16 @@
         <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
         <v>77</v>
       </c>
@@ -9658,13 +9631,13 @@
         <v>77</v>
       </c>
       <c r="W70" t="s" s="2">
-        <v>273</v>
+        <v>107</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>77</v>
@@ -9682,7 +9655,7 @@
         <v>77</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>75</v>
@@ -9700,18 +9673,18 @@
         <v>77</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
@@ -9722,7 +9695,7 @@
         <v>75</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>77</v>
@@ -9734,13 +9707,13 @@
         <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>179</v>
+        <v>417</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
@@ -9767,13 +9740,13 @@
         <v>77</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>454</v>
+        <v>77</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>455</v>
+        <v>77</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>77</v>
@@ -9791,13 +9764,13 @@
         <v>77</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>77</v>
@@ -9809,18 +9782,18 @@
         <v>77</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -9831,7 +9804,7 @@
         <v>75</v>
       </c>
       <c r="F72" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>77</v>
@@ -9843,13 +9816,13 @@
         <v>77</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
@@ -9876,37 +9849,37 @@
         <v>77</v>
       </c>
       <c r="W72" t="s" s="2">
-        <v>107</v>
+        <v>265</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE72" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>458</v>
-      </c>
       <c r="AF72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>77</v>
@@ -9918,18 +9891,18 @@
         <v>77</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -9940,7 +9913,7 @@
         <v>75</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>77</v>
@@ -9952,15 +9925,17 @@
         <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="M73" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
         <v>77</v>
@@ -10009,13 +9984,13 @@
         <v>77</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>77</v>
@@ -10027,18 +10002,18 @@
         <v>77</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>469</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
@@ -10061,13 +10036,13 @@
         <v>77</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>471</v>
+        <v>150</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>472</v>
+        <v>151</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -10094,13 +10069,13 @@
         <v>77</v>
       </c>
       <c r="W74" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>473</v>
+        <v>77</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>474</v>
+        <v>77</v>
       </c>
       <c r="Z74" t="s" s="2">
         <v>77</v>
@@ -10118,7 +10093,7 @@
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>470</v>
+        <v>152</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>75</v>
@@ -10130,28 +10105,28 @@
         <v>77</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>475</v>
+        <v>153</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>476</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10170,16 +10145,16 @@
         <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>233</v>
+        <v>129</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>478</v>
+        <v>130</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>479</v>
+        <v>155</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>480</v>
+        <v>132</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
@@ -10229,7 +10204,7 @@
         <v>77</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>477</v>
+        <v>159</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>75</v>
@@ -10241,13 +10216,13 @@
         <v>77</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>481</v>
+        <v>153</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>77</v>
@@ -10258,39 +10233,43 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F76" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>159</v>
+        <v>233</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="M76" s="2"/>
-      <c r="N76" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O76" t="s" s="2">
         <v>77</v>
       </c>
@@ -10338,25 +10317,25 @@
         <v>77</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>77</v>
@@ -10367,18 +10346,18 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F77" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>77</v>
@@ -10390,17 +10369,15 @@
         <v>77</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>128</v>
+        <v>478</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>164</v>
+        <v>479</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="M77" s="2"/>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
         <v>77</v>
@@ -10449,31 +10426,31 @@
         <v>77</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>167</v>
+        <v>477</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>77</v>
+        <v>481</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>162</v>
+        <v>335</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>77</v>
+        <v>482</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>77</v>
+        <v>483</v>
       </c>
     </row>
     <row r="78" hidden="true">
@@ -10482,39 +10459,37 @@
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>240</v>
+        <v>77</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F78" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>241</v>
+        <v>485</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>242</v>
+        <v>486</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
         <v>77</v>
       </c>
@@ -10538,13 +10513,13 @@
         <v>77</v>
       </c>
       <c r="W78" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>77</v>
+        <v>488</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>77</v>
+        <v>489</v>
       </c>
       <c r="Z78" t="s" s="2">
         <v>77</v>
@@ -10562,25 +10537,25 @@
         <v>77</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>243</v>
+        <v>484</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>126</v>
+        <v>490</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>77</v>
@@ -10591,7 +10566,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
@@ -10599,7 +10574,7 @@
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F79" t="s" s="2">
         <v>83</v>
@@ -10614,15 +10589,17 @@
         <v>77</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>486</v>
+        <v>171</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="M79" s="2"/>
+        <v>493</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>494</v>
+      </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
         <v>77</v>
@@ -10647,13 +10624,13 @@
         <v>77</v>
       </c>
       <c r="W79" t="s" s="2">
-        <v>77</v>
+        <v>265</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>77</v>
+        <v>495</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>77</v>
+        <v>496</v>
       </c>
       <c r="Z79" t="s" s="2">
         <v>77</v>
@@ -10671,10 +10648,10 @@
         <v>77</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -10686,21 +10663,21 @@
         <v>95</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>489</v>
+        <v>77</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>343</v>
+        <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>490</v>
+        <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>491</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
@@ -10723,17 +10700,15 @@
         <v>77</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="M80" s="2"/>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
         <v>77</v>
@@ -10758,31 +10733,31 @@
         <v>77</v>
       </c>
       <c r="W80" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>496</v>
+        <v>77</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE80" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>75</v>
@@ -10800,7 +10775,7 @@
         <v>77</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>498</v>
+        <v>328</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>77</v>
@@ -10811,7 +10786,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
@@ -10834,17 +10809,15 @@
         <v>77</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="M81" t="s" s="2">
         <v>502</v>
       </c>
+      <c r="M81" s="2"/>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
         <v>77</v>
@@ -10869,13 +10842,13 @@
         <v>77</v>
       </c>
       <c r="W81" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>503</v>
+        <v>77</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>504</v>
+        <v>77</v>
       </c>
       <c r="Z81" t="s" s="2">
         <v>77</v>
@@ -10893,7 +10866,7 @@
         <v>77</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>75</v>
@@ -10908,16 +10881,16 @@
         <v>95</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>77</v>
+        <v>334</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>77</v>
+        <v>503</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>77</v>
+        <v>504</v>
       </c>
     </row>
     <row r="82" hidden="true">
@@ -10945,15 +10918,17 @@
         <v>77</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>207</v>
+        <v>506</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="M82" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>509</v>
+      </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
         <v>77</v>
@@ -11017,240 +10992,20 @@
         <v>95</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>77</v>
+        <v>510</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>336</v>
+        <v>511</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="B83" s="2"/>
-      <c r="C83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="D83" s="2"/>
-      <c r="E83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="M83" s="2"/>
-      <c r="N83" s="2"/>
-      <c r="O83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="P83" s="2"/>
-      <c r="Q83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="R83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="B84" s="2"/>
-      <c r="C84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="D84" s="2"/>
-      <c r="E84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="P84" s="2"/>
-      <c r="Q84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="R84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM84" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM84">
+  <autoFilter ref="A1:AM82">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11260,7 +11015,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI83">
+  <conditionalFormatting sqref="A2:AI81">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T15:13:04+00:00</t>
+    <t>2023-03-02T20:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T20:01:22+00:00</t>
+    <t>2023-03-03T15:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-03T15:04:24+00:00</t>
+    <t>2023-03-06T14:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-06T14:18:09+00:00</t>
+    <t>2023-03-08T00:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:16:35+00:00</t>
+    <t>2023-03-08T00:32:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$98</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2881" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3439" uniqueCount="523">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:32:01+00:00</t>
+    <t>2023-03-09T19:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -901,7 +901,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PatientLE)
 </t>
   </si>
   <si>
@@ -1164,6 +1164,9 @@
     <t>Encounter.reasonReference</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reference(Condition|Procedure|Observation|ImmunizationRecommendation)
 </t>
   </si>
@@ -1171,6 +1174,27 @@
     <t>Reason the encounter takes place (reference)</t>
   </si>
   <si>
+    <t xml:space="preserve">value:reference}
+</t>
+  </si>
+  <si>
+    <t>Slice creado para almacenar diferentes tipos de reasonReference</t>
+  </si>
+  <si>
+    <t>CondicionAtenderDiagnosticoConfirmacionLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/CondicionAtenderDiagnosticoConfirmacionLE)
+</t>
+  </si>
+  <si>
+    <t>ObservationAtenderLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/ObservationAtenderLE)
+</t>
+  </si>
+  <si>
     <t>Encounter.diagnosis</t>
   </si>
   <si>
@@ -1247,6 +1271,20 @@
   </si>
   <si>
     <t>.outboundRelationship[typeCode=RSON].priority</t>
+  </si>
+  <si>
+    <t>CondicionAtenderDiagnosticoSospechaLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/CondicionAtenderDiagnosticoSospechaLE)
+</t>
+  </si>
+  <si>
+    <t>CondicionAtenderHipotesisDiagnosticaCodigoLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/CondicionAtenderHipotesisDiagnosticaCodigoLE)
+</t>
   </si>
   <si>
     <t>Encounter.account</t>
@@ -1906,11 +1944,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM82"/>
+  <dimension ref="A1:AM98"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.67578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.66015625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.17578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1936,7 +1974,7 @@
     <col min="25" max="25" width="56.25390625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="42.03515625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="61.2734375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.4140625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="45.67578125" customWidth="true" bestFit="true" hidden="true"/>
@@ -5936,7 +5974,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>284</v>
       </c>
@@ -5946,13 +5984,13 @@
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
@@ -7488,13 +7526,13 @@
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
-        <v>75</v>
+        <v>371</v>
       </c>
       <c r="F51" t="s" s="2">
-        <v>76</v>
+        <v>371</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -7503,10 +7541,10 @@
         <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>362</v>
@@ -7550,16 +7588,16 @@
         <v>77</v>
       </c>
       <c r="AA51" t="s" s="2">
-        <v>77</v>
+        <v>374</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>77</v>
+        <v>375</v>
       </c>
       <c r="AC51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AD51" t="s" s="2">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="AE51" t="s" s="2">
         <v>370</v>
@@ -7589,23 +7627,25 @@
         <v>369</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="B52" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="C52" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F52" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7614,15 +7654,17 @@
         <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>225</v>
+        <v>377</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="M52" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
         <v>77</v>
@@ -7671,7 +7713,7 @@
         <v>77</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>75</v>
@@ -7686,52 +7728,56 @@
         <v>95</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>77</v>
+        <v>366</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>77</v>
+        <v>369</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="B53" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="C53" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>149</v>
+        <v>379</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>150</v>
+        <v>373</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M53" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
         <v>77</v>
@@ -7780,69 +7826,67 @@
         <v>77</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>152</v>
+        <v>370</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>77</v>
+        <v>366</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>153</v>
+        <v>367</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>77</v>
+        <v>369</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
-        <v>75</v>
+        <v>371</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>76</v>
+        <v>371</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>130</v>
+        <v>381</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="M54" s="2"/>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
         <v>77</v>
@@ -7879,19 +7923,19 @@
         <v>77</v>
       </c>
       <c r="AA54" t="s" s="2">
-        <v>77</v>
+        <v>374</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>77</v>
+        <v>375</v>
       </c>
       <c r="AC54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AD54" t="s" s="2">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>159</v>
+        <v>380</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>75</v>
@@ -7903,13 +7947,13 @@
         <v>77</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>153</v>
+        <v>383</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>77</v>
@@ -7920,43 +7964,39 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>233</v>
+        <v>150</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
         <v>77</v>
       </c>
@@ -8004,25 +8044,25 @@
         <v>77</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>235</v>
+        <v>152</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>77</v>
@@ -8033,18 +8073,18 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
-        <v>381</v>
+        <v>128</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>77</v>
@@ -8053,19 +8093,19 @@
         <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>382</v>
+        <v>129</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>383</v>
+        <v>130</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>384</v>
+        <v>155</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>363</v>
+        <v>132</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
@@ -8115,68 +8155,72 @@
         <v>77</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>380</v>
+        <v>159</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>385</v>
+        <v>77</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>386</v>
+        <v>153</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>387</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>389</v>
+        <v>233</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8200,13 +8244,13 @@
         <v>77</v>
       </c>
       <c r="W57" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>391</v>
+        <v>77</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>392</v>
+        <v>77</v>
       </c>
       <c r="Z57" t="s" s="2">
         <v>77</v>
@@ -8224,25 +8268,25 @@
         <v>77</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>388</v>
+        <v>235</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>77</v>
@@ -8253,15 +8297,15 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>77</v>
+        <v>388</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>83</v>
@@ -8273,18 +8317,20 @@
         <v>77</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="M58" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
         <v>77</v>
@@ -8333,10 +8379,10 @@
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -8348,21 +8394,21 @@
         <v>95</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>77</v>
+        <v>392</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>77</v>
+        <v>394</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8373,7 +8419,7 @@
         <v>75</v>
       </c>
       <c r="F59" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>77</v>
@@ -8385,17 +8431,15 @@
         <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>399</v>
+        <v>171</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="M59" s="2"/>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
         <v>77</v>
@@ -8420,13 +8464,13 @@
         <v>77</v>
       </c>
       <c r="W59" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>77</v>
+        <v>398</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>77</v>
+        <v>399</v>
       </c>
       <c r="Z59" t="s" s="2">
         <v>77</v>
@@ -8444,13 +8488,13 @@
         <v>77</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>77</v>
@@ -8462,7 +8506,7 @@
         <v>77</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>403</v>
+        <v>153</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>77</v>
@@ -8473,7 +8517,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -8496,17 +8540,15 @@
         <v>77</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>225</v>
+        <v>401</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="M60" s="2"/>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
         <v>77</v>
@@ -8555,7 +8597,7 @@
         <v>77</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>75</v>
@@ -8573,7 +8615,7 @@
         <v>77</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>77</v>
@@ -8582,38 +8624,40 @@
         <v>77</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="B61" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="C61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>149</v>
+        <v>225</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>150</v>
+        <v>381</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>151</v>
+        <v>382</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
@@ -8664,25 +8708,25 @@
         <v>77</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>152</v>
+        <v>380</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>153</v>
+        <v>383</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>77</v>
@@ -8693,18 +8737,18 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F62" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>77</v>
@@ -8716,17 +8760,15 @@
         <v>77</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="M62" s="2"/>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
         <v>77</v>
@@ -8775,19 +8817,19 @@
         <v>77</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>77</v>
@@ -8804,11 +8846,11 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>411</v>
+        <v>385</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
-        <v>232</v>
+        <v>128</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -8821,26 +8863,24 @@
         <v>77</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>129</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>233</v>
+        <v>130</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>234</v>
+        <v>155</v>
       </c>
       <c r="M63" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="N63" t="s" s="2">
-        <v>138</v>
-      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
         <v>77</v>
       </c>
@@ -8888,7 +8928,7 @@
         <v>77</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>235</v>
+        <v>159</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>75</v>
@@ -8906,7 +8946,7 @@
         <v>77</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>77</v>
@@ -8917,39 +8957,43 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F64" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>413</v>
+        <v>233</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="M64" s="2"/>
-      <c r="N64" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O64" t="s" s="2">
         <v>77</v>
       </c>
@@ -8997,44 +9041,44 @@
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>412</v>
+        <v>235</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>415</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>416</v>
+        <v>387</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
-        <v>77</v>
+        <v>388</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>83</v>
@@ -9046,18 +9090,20 @@
         <v>77</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>418</v>
+        <v>390</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="M65" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
         <v>77</v>
@@ -9106,10 +9152,10 @@
         <v>77</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>416</v>
+        <v>387</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -9121,21 +9167,21 @@
         <v>95</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>77</v>
+        <v>392</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>420</v>
+        <v>393</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>77</v>
+        <v>394</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9161,10 +9207,10 @@
         <v>171</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>422</v>
+        <v>396</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -9194,10 +9240,10 @@
         <v>107</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>424</v>
+        <v>398</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="Z66" t="s" s="2">
         <v>77</v>
@@ -9215,7 +9261,7 @@
         <v>77</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>75</v>
@@ -9233,18 +9279,18 @@
         <v>77</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>426</v>
+        <v>153</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>427</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>428</v>
+        <v>400</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
@@ -9267,13 +9313,13 @@
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>171</v>
+        <v>401</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>429</v>
+        <v>402</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>430</v>
+        <v>403</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -9300,13 +9346,13 @@
         <v>77</v>
       </c>
       <c r="W67" t="s" s="2">
-        <v>265</v>
+        <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>431</v>
+        <v>77</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>432</v>
+        <v>77</v>
       </c>
       <c r="Z67" t="s" s="2">
         <v>77</v>
@@ -9324,7 +9370,7 @@
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>428</v>
+        <v>400</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>75</v>
@@ -9342,54 +9388,52 @@
         <v>77</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>153</v>
+        <v>404</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>433</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="B68" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="C68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>171</v>
+        <v>225</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>435</v>
+        <v>381</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
         <v>77</v>
       </c>
@@ -9413,13 +9457,13 @@
         <v>77</v>
       </c>
       <c r="W68" t="s" s="2">
-        <v>265</v>
+        <v>77</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>439</v>
+        <v>77</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>440</v>
+        <v>77</v>
       </c>
       <c r="Z68" t="s" s="2">
         <v>77</v>
@@ -9437,7 +9481,7 @@
         <v>77</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>434</v>
+        <v>380</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>75</v>
@@ -9455,18 +9499,18 @@
         <v>77</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>441</v>
+        <v>383</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>442</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>443</v>
+        <v>384</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
@@ -9477,7 +9521,7 @@
         <v>75</v>
       </c>
       <c r="F69" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>77</v>
@@ -9489,13 +9533,13 @@
         <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>444</v>
+        <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>445</v>
+        <v>151</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -9522,13 +9566,13 @@
         <v>77</v>
       </c>
       <c r="W69" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>446</v>
+        <v>77</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>447</v>
+        <v>77</v>
       </c>
       <c r="Z69" t="s" s="2">
         <v>77</v>
@@ -9546,40 +9590,40 @@
         <v>77</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>443</v>
+        <v>152</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>448</v>
+        <v>153</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>449</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>450</v>
+        <v>385</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -9598,15 +9642,17 @@
         <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>451</v>
+        <v>130</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="M70" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
         <v>77</v>
@@ -9631,13 +9677,13 @@
         <v>77</v>
       </c>
       <c r="W70" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>453</v>
+        <v>77</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>454</v>
+        <v>77</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>77</v>
@@ -9655,7 +9701,7 @@
         <v>77</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>450</v>
+        <v>159</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>75</v>
@@ -9667,56 +9713,60 @@
         <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>455</v>
+        <v>153</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>456</v>
+        <v>77</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>457</v>
+        <v>386</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>417</v>
+        <v>129</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>458</v>
+        <v>233</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="M71" s="2"/>
-      <c r="N71" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O71" t="s" s="2">
         <v>77</v>
       </c>
@@ -9764,44 +9814,44 @@
         <v>77</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>457</v>
+        <v>235</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>460</v>
+        <v>126</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>461</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>462</v>
+        <v>387</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
-        <v>77</v>
+        <v>388</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F72" t="s" s="2">
         <v>83</v>
@@ -9813,18 +9863,20 @@
         <v>77</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>171</v>
+        <v>408</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>463</v>
+        <v>390</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="M72" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
         <v>77</v>
@@ -9849,13 +9901,13 @@
         <v>77</v>
       </c>
       <c r="W72" t="s" s="2">
-        <v>265</v>
+        <v>77</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>465</v>
+        <v>77</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>466</v>
+        <v>77</v>
       </c>
       <c r="Z72" t="s" s="2">
         <v>77</v>
@@ -9873,10 +9925,10 @@
         <v>77</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>462</v>
+        <v>387</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -9888,21 +9940,21 @@
         <v>95</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>77</v>
+        <v>392</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>467</v>
+        <v>393</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>468</v>
+        <v>394</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>469</v>
+        <v>395</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -9913,7 +9965,7 @@
         <v>75</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>77</v>
@@ -9925,17 +9977,15 @@
         <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>225</v>
+        <v>171</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>470</v>
+        <v>396</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="M73" s="2"/>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
         <v>77</v>
@@ -9960,13 +10010,13 @@
         <v>77</v>
       </c>
       <c r="W73" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>77</v>
+        <v>398</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>77</v>
+        <v>399</v>
       </c>
       <c r="Z73" t="s" s="2">
         <v>77</v>
@@ -9984,13 +10034,13 @@
         <v>77</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>469</v>
+        <v>395</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>77</v>
@@ -10002,7 +10052,7 @@
         <v>77</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>473</v>
+        <v>153</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>77</v>
@@ -10013,7 +10063,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>474</v>
+        <v>400</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
@@ -10036,13 +10086,13 @@
         <v>77</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>149</v>
+        <v>401</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>151</v>
+        <v>403</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -10093,7 +10143,7 @@
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>152</v>
+        <v>400</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>75</v>
@@ -10105,13 +10155,13 @@
         <v>77</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>153</v>
+        <v>404</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>77</v>
@@ -10122,11 +10172,11 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>475</v>
+        <v>409</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10145,16 +10195,16 @@
         <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>129</v>
+        <v>410</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>130</v>
+        <v>411</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>155</v>
+        <v>412</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>132</v>
+        <v>413</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
@@ -10204,7 +10254,7 @@
         <v>77</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>159</v>
+        <v>409</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>75</v>
@@ -10216,13 +10266,13 @@
         <v>77</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>153</v>
+        <v>414</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>77</v>
@@ -10233,43 +10283,41 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>476</v>
+        <v>415</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F76" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>233</v>
+        <v>416</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>234</v>
+        <v>417</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
         <v>77</v>
       </c>
@@ -10317,25 +10365,25 @@
         <v>77</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>235</v>
+        <v>415</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>126</v>
+        <v>419</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>77</v>
@@ -10346,7 +10394,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>477</v>
+        <v>420</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
@@ -10354,7 +10402,7 @@
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F77" t="s" s="2">
         <v>83</v>
@@ -10369,13 +10417,13 @@
         <v>77</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>478</v>
+        <v>149</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>479</v>
+        <v>150</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>480</v>
+        <v>151</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -10426,10 +10474,10 @@
         <v>77</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>477</v>
+        <v>152</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -10438,35 +10486,35 @@
         <v>77</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>481</v>
+        <v>77</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>335</v>
+        <v>153</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>482</v>
+        <v>77</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>483</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>484</v>
+        <v>421</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F78" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>77</v>
@@ -10478,16 +10526,16 @@
         <v>77</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>485</v>
+        <v>130</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>486</v>
+        <v>155</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>487</v>
+        <v>132</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
@@ -10513,13 +10561,13 @@
         <v>77</v>
       </c>
       <c r="W78" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>488</v>
+        <v>77</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>489</v>
+        <v>77</v>
       </c>
       <c r="Z78" t="s" s="2">
         <v>77</v>
@@ -10537,25 +10585,25 @@
         <v>77</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>484</v>
+        <v>159</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>490</v>
+        <v>153</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>77</v>
@@ -10566,41 +10614,43 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>491</v>
+        <v>422</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F79" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>492</v>
+        <v>233</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>493</v>
+        <v>234</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O79" t="s" s="2">
         <v>77</v>
       </c>
@@ -10624,13 +10674,13 @@
         <v>77</v>
       </c>
       <c r="W79" t="s" s="2">
-        <v>265</v>
+        <v>77</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>495</v>
+        <v>77</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>496</v>
+        <v>77</v>
       </c>
       <c r="Z79" t="s" s="2">
         <v>77</v>
@@ -10648,25 +10698,25 @@
         <v>77</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>491</v>
+        <v>235</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>77</v>
@@ -10677,7 +10727,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>497</v>
+        <v>423</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
@@ -10700,13 +10750,13 @@
         <v>77</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>199</v>
+        <v>141</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>498</v>
+        <v>424</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>499</v>
+        <v>425</v>
       </c>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
@@ -10757,7 +10807,7 @@
         <v>77</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>497</v>
+        <v>423</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>75</v>
@@ -10775,18 +10825,18 @@
         <v>77</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>328</v>
+        <v>145</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>77</v>
+        <v>426</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>500</v>
+        <v>427</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
@@ -10809,13 +10859,13 @@
         <v>77</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>206</v>
+        <v>428</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>501</v>
+        <v>429</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>502</v>
+        <v>430</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -10866,7 +10916,7 @@
         <v>77</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>500</v>
+        <v>427</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>75</v>
@@ -10881,21 +10931,21 @@
         <v>95</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>334</v>
+        <v>77</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>503</v>
+        <v>431</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>504</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>505</v>
+        <v>432</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
@@ -10918,17 +10968,15 @@
         <v>77</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>506</v>
+        <v>171</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>507</v>
+        <v>433</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>509</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="M82" s="2"/>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
         <v>77</v>
@@ -10953,13 +11001,13 @@
         <v>77</v>
       </c>
       <c r="W82" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>77</v>
+        <v>435</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>77</v>
+        <v>436</v>
       </c>
       <c r="Z82" t="s" s="2">
         <v>77</v>
@@ -10977,7 +11025,7 @@
         <v>77</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>505</v>
+        <v>432</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>75</v>
@@ -10992,20 +11040,1782 @@
         <v>95</v>
       </c>
       <c r="AJ82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B83" s="2"/>
+      <c r="C83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D83" s="2"/>
+      <c r="E83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M83" s="2"/>
+      <c r="N83" s="2"/>
+      <c r="O83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P83" s="2"/>
+      <c r="Q83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B84" s="2"/>
+      <c r="C84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D84" s="2"/>
+      <c r="E84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P84" s="2"/>
+      <c r="Q84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B85" s="2"/>
+      <c r="C85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D85" s="2"/>
+      <c r="E85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M85" s="2"/>
+      <c r="N85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P85" s="2"/>
+      <c r="Q85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B86" s="2"/>
+      <c r="C86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D86" s="2"/>
+      <c r="E86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M86" s="2"/>
+      <c r="N86" s="2"/>
+      <c r="O86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P86" s="2"/>
+      <c r="Q86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B87" s="2"/>
+      <c r="C87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D87" s="2"/>
+      <c r="E87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F87" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M87" s="2"/>
+      <c r="N87" s="2"/>
+      <c r="O87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P87" s="2"/>
+      <c r="Q87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B88" s="2"/>
+      <c r="C88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D88" s="2"/>
+      <c r="E88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M88" s="2"/>
+      <c r="N88" s="2"/>
+      <c r="O88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P88" s="2"/>
+      <c r="Q88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B89" s="2"/>
+      <c r="C89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D89" s="2"/>
+      <c r="E89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P89" s="2"/>
+      <c r="Q89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B90" s="2"/>
+      <c r="C90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D90" s="2"/>
+      <c r="E90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F90" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M90" s="2"/>
+      <c r="N90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P90" s="2"/>
+      <c r="Q90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B91" s="2"/>
+      <c r="C91" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="D91" s="2"/>
+      <c r="E91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P91" s="2"/>
+      <c r="Q91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B92" s="2"/>
+      <c r="C92" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="D92" s="2"/>
+      <c r="E92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F92" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P92" s="2"/>
+      <c r="Q92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B93" s="2"/>
+      <c r="C93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D93" s="2"/>
+      <c r="E93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="F93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M93" s="2"/>
+      <c r="N93" s="2"/>
+      <c r="O93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P93" s="2"/>
+      <c r="Q93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B94" s="2"/>
+      <c r="C94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D94" s="2"/>
+      <c r="E94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P94" s="2"/>
+      <c r="Q94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B95" s="2"/>
+      <c r="C95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D95" s="2"/>
+      <c r="E95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P95" s="2"/>
+      <c r="Q95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B96" s="2"/>
+      <c r="C96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D96" s="2"/>
+      <c r="E96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="AK82" t="s" s="2">
+      <c r="M96" s="2"/>
+      <c r="N96" s="2"/>
+      <c r="O96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P96" s="2"/>
+      <c r="Q96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AL82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM82" t="s" s="2">
+      <c r="B97" s="2"/>
+      <c r="C97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D97" s="2"/>
+      <c r="E97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M97" s="2"/>
+      <c r="N97" s="2"/>
+      <c r="O97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P97" s="2"/>
+      <c r="Q97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B98" s="2"/>
+      <c r="C98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D98" s="2"/>
+      <c r="E98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P98" s="2"/>
+      <c r="Q98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM98" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM82">
+  <autoFilter ref="A1:AM98">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11015,7 +12825,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI81">
+  <conditionalFormatting sqref="A2:AI97">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:11:45+00:00</t>
+    <t>2023-03-09T19:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:22:45+00:00</t>
+    <t>2023-03-09T19:42:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$102</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3439" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3578" uniqueCount="543">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:42:39+00:00</t>
+    <t>2023-03-10T17:11:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -774,46 +774,49 @@
     <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
   </si>
   <si>
+    <t>http://minsal.cl/listaespera/ValueSet/VSTipoConsulta</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>PV1-2</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory</t>
+  </si>
+  <si>
+    <t>List of past encounter classes</t>
+  </si>
+  <si>
+    <t>The class history permits the tracking of the encounters transitions without needing to go  through the resource history.  This would be used for a case where an admission starts of as an emergency encounter, then transitions into an inpatient scenario. Doing this and not restarting a new encounter ensures that any lab/diagnostic results can more easily follow the patient and not require re-processing and not get lost or cancelled during a kind of discharge from emergency to inpatient.</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.id</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.extension</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.modifierExtension</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.class</t>
+  </si>
+  <si>
+    <t>inpatient | outpatient | ambulatory | emergency +</t>
+  </si>
+  <si>
+    <t>inpatient | outpatient | ambulatory | emergency +.</t>
+  </si>
+  <si>
     <t>Classification of the encounter.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>PV1-2</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory</t>
-  </si>
-  <si>
-    <t>List of past encounter classes</t>
-  </si>
-  <si>
-    <t>The class history permits the tracking of the encounters transitions without needing to go  through the resource history.  This would be used for a case where an admission starts of as an emergency encounter, then transitions into an inpatient scenario. Doing this and not restarting a new encounter ensures that any lab/diagnostic results can more easily follow the patient and not require re-processing and not get lost or cancelled during a kind of discharge from emergency to inpatient.</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.id</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.extension</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.modifierExtension</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.class</t>
-  </si>
-  <si>
-    <t>inpatient | outpatient | ambulatory | emergency +</t>
-  </si>
-  <si>
-    <t>inpatient | outpatient | ambulatory | emergency +.</t>
   </si>
   <si>
     <t>Encounter.classHistory.period</t>
@@ -1103,6 +1106,65 @@
   </si>
   <si>
     <t>PV1-44, PV1-45</t>
+  </si>
+  <si>
+    <t>Encounter.period.id</t>
+  </si>
+  <si>
+    <t>Encounter.period.extension</t>
+  </si>
+  <si>
+    <t>Encounter.period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per-1
+</t>
+  </si>
+  <si>
+    <t>./low</t>
+  </si>
+  <si>
+    <t>DR.1</t>
+  </si>
+  <si>
+    <t>Encounter.period.end</t>
+  </si>
+  <si>
+    <t>End time with inclusive boundary, if not ongoing</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+  </si>
+  <si>
+    <t>If the end of the period is missing, it means that the period is ongoing</t>
+  </si>
+  <si>
+    <t>Period.end</t>
+  </si>
+  <si>
+    <t>./high</t>
+  </si>
+  <si>
+    <t>DR.2</t>
   </si>
   <si>
     <t>Encounter.length</t>
@@ -1944,7 +2006,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM98"/>
+  <dimension ref="A1:AM102"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.67578125" customWidth="true" bestFit="true"/>
@@ -4934,13 +4996,11 @@
         <v>77</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="X27" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="X27" s="2"/>
+      <c r="Y27" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>77</v>
@@ -4976,18 +5036,18 @@
         <v>77</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>248</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -5013,10 +5073,10 @@
         <v>225</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -5067,7 +5127,7 @@
         <v>77</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>75</v>
@@ -5096,7 +5156,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5205,7 +5265,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5316,7 +5376,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5429,7 +5489,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -5455,10 +5515,10 @@
         <v>241</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -5488,10 +5548,10 @@
         <v>176</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>77</v>
@@ -5509,7 +5569,7 @@
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>83</v>
@@ -5538,7 +5598,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -5564,10 +5624,10 @@
         <v>199</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -5618,7 +5678,7 @@
         <v>77</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>83</v>
@@ -5647,7 +5707,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5673,13 +5733,13 @@
         <v>171</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
@@ -5705,13 +5765,13 @@
         <v>77</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>77</v>
@@ -5729,7 +5789,7 @@
         <v>77</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>75</v>
@@ -5744,21 +5804,21 @@
         <v>95</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5784,10 +5844,10 @@
         <v>171</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -5814,13 +5874,13 @@
         <v>77</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>77</v>
@@ -5838,7 +5898,7 @@
         <v>77</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>75</v>
@@ -5853,7 +5913,7 @@
         <v>95</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>153</v>
@@ -5862,12 +5922,12 @@
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -5893,10 +5953,10 @@
         <v>171</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
@@ -5923,13 +5983,13 @@
         <v>77</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Z36" t="s" s="2">
         <v>77</v>
@@ -5947,7 +6007,7 @@
         <v>77</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>75</v>
@@ -5965,22 +6025,22 @@
         <v>77</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -5999,16 +6059,16 @@
         <v>84</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
@@ -6058,7 +6118,7 @@
         <v>77</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>75</v>
@@ -6073,21 +6133,21 @@
         <v>95</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6110,13 +6170,13 @@
         <v>84</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -6167,7 +6227,7 @@
         <v>77</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>75</v>
@@ -6182,25 +6242,25 @@
         <v>95</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>153</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6219,13 +6279,13 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
@@ -6276,7 +6336,7 @@
         <v>77</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>75</v>
@@ -6291,10 +6351,10 @@
         <v>95</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
@@ -6305,7 +6365,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6331,10 +6391,10 @@
         <v>225</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -6385,7 +6445,7 @@
         <v>77</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>75</v>
@@ -6400,21 +6460,21 @@
         <v>95</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -6523,7 +6583,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6634,7 +6694,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -6747,7 +6807,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -6773,13 +6833,13 @@
         <v>171</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
@@ -6808,10 +6868,10 @@
         <v>176</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Z44" t="s" s="2">
         <v>77</v>
@@ -6829,7 +6889,7 @@
         <v>77</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>75</v>
@@ -6844,21 +6904,21 @@
         <v>95</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -6884,10 +6944,10 @@
         <v>199</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
@@ -6938,7 +6998,7 @@
         <v>77</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>75</v>
@@ -6956,18 +7016,18 @@
         <v>77</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -6990,13 +7050,13 @@
         <v>84</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -7047,7 +7107,7 @@
         <v>77</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>75</v>
@@ -7062,21 +7122,21 @@
         <v>95</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -7099,13 +7159,13 @@
         <v>84</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -7156,7 +7216,7 @@
         <v>77</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>75</v>
@@ -7171,21 +7231,21 @@
         <v>95</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -7211,13 +7271,13 @@
         <v>199</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
@@ -7267,7 +7327,7 @@
         <v>77</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>75</v>
@@ -7279,24 +7339,24 @@
         <v>77</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -7319,17 +7379,15 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>353</v>
+        <v>149</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>354</v>
+        <v>150</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
         <v>77</v>
@@ -7378,7 +7436,7 @@
         <v>77</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>352</v>
+        <v>152</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>75</v>
@@ -7390,28 +7448,28 @@
         <v>77</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>348</v>
+        <v>77</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>357</v>
+        <v>153</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>358</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>360</v>
+        <v>128</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7427,19 +7485,19 @@
         <v>77</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>361</v>
+        <v>130</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>362</v>
+        <v>155</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>363</v>
+        <v>132</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
@@ -7465,31 +7523,31 @@
         <v>77</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>364</v>
+        <v>77</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>365</v>
+        <v>77</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AA50" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="AC50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AD50" t="s" s="2">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>359</v>
+        <v>159</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>75</v>
@@ -7501,35 +7559,35 @@
         <v>77</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>366</v>
+        <v>77</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>367</v>
+        <v>153</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>369</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="F51" t="s" s="2">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>84</v>
@@ -7541,16 +7599,16 @@
         <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
@@ -7588,64 +7646,62 @@
         <v>77</v>
       </c>
       <c r="AA51" t="s" s="2">
-        <v>374</v>
+        <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>375</v>
+        <v>77</v>
       </c>
       <c r="AC51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AD51" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>366</v>
+        <v>77</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7654,22 +7710,24 @@
         <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>377</v>
+        <v>356</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="P52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="Q52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7713,70 +7771,68 @@
         <v>77</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>366</v>
+        <v>77</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
@@ -7826,13 +7882,13 @@
         <v>77</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>77</v>
@@ -7841,35 +7897,35 @@
         <v>95</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>77</v>
+        <v>380</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
-        <v>371</v>
+        <v>75</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>371</v>
+        <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -7878,7 +7934,7 @@
         <v>84</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>225</v>
+        <v>171</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>381</v>
@@ -7886,7 +7942,9 @@
       <c r="L54" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M54" s="2"/>
+      <c r="M54" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
         <v>77</v>
@@ -7911,31 +7969,31 @@
         <v>77</v>
       </c>
       <c r="W54" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>77</v>
+        <v>384</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>77</v>
+        <v>385</v>
       </c>
       <c r="Z54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AA54" t="s" s="2">
-        <v>374</v>
+        <v>77</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>375</v>
+        <v>77</v>
       </c>
       <c r="AC54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AD54" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>75</v>
@@ -7950,52 +8008,54 @@
         <v>95</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>77</v>
+        <v>386</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>77</v>
+        <v>388</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>77</v>
+        <v>389</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>77</v>
+        <v>380</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
-        <v>75</v>
+        <v>391</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>149</v>
+        <v>392</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>150</v>
+        <v>393</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M55" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
         <v>77</v>
@@ -8032,80 +8092,82 @@
         <v>77</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>77</v>
+        <v>394</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>77</v>
+        <v>395</v>
       </c>
       <c r="AC55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AD55" t="s" s="2">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>152</v>
+        <v>390</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>77</v>
+        <v>386</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>153</v>
+        <v>387</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>77</v>
+        <v>388</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>77</v>
+        <v>389</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="B56" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="C56" t="s" s="2">
-        <v>128</v>
+        <v>380</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>129</v>
+        <v>397</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>130</v>
+        <v>393</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>155</v>
+        <v>382</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>132</v>
+        <v>383</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
@@ -8155,7 +8217,7 @@
         <v>77</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>159</v>
+        <v>390</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>75</v>
@@ -8167,60 +8229,60 @@
         <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>77</v>
+        <v>386</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>153</v>
+        <v>387</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>77</v>
+        <v>388</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>77</v>
+        <v>389</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="B57" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="C57" t="s" s="2">
-        <v>232</v>
+        <v>380</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>129</v>
+        <v>399</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>233</v>
+        <v>393</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>234</v>
+        <v>382</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8268,7 +8330,7 @@
         <v>77</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>235</v>
+        <v>390</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>75</v>
@@ -8280,38 +8342,38 @@
         <v>77</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>77</v>
+        <v>386</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>126</v>
+        <v>387</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>77</v>
+        <v>388</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>77</v>
+        <v>389</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>388</v>
+        <v>77</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8320,17 +8382,15 @@
         <v>84</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>389</v>
+        <v>225</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="M58" s="2"/>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
         <v>77</v>
@@ -8367,25 +8427,25 @@
         <v>77</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>77</v>
+        <v>394</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>77</v>
+        <v>395</v>
       </c>
       <c r="AC58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AD58" t="s" s="2">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>77</v>
@@ -8394,21 +8454,21 @@
         <v>95</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>392</v>
+        <v>77</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>394</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8431,13 +8491,13 @@
         <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>396</v>
+        <v>150</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>397</v>
+        <v>151</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -8464,13 +8524,13 @@
         <v>77</v>
       </c>
       <c r="W59" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>398</v>
+        <v>77</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>399</v>
+        <v>77</v>
       </c>
       <c r="Z59" t="s" s="2">
         <v>77</v>
@@ -8488,7 +8548,7 @@
         <v>77</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>395</v>
+        <v>152</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>75</v>
@@ -8500,7 +8560,7 @@
         <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>77</v>
@@ -8517,18 +8577,18 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F60" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>77</v>
@@ -8540,15 +8600,17 @@
         <v>77</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>401</v>
+        <v>129</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>402</v>
+        <v>130</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="M60" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
         <v>77</v>
@@ -8597,25 +8659,25 @@
         <v>77</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>400</v>
+        <v>159</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>404</v>
+        <v>153</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>77</v>
@@ -8624,43 +8686,45 @@
         <v>77</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F61" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H61" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>225</v>
+        <v>129</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>381</v>
+        <v>233</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="M61" s="2"/>
-      <c r="N61" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O61" t="s" s="2">
         <v>77</v>
       </c>
@@ -8708,7 +8772,7 @@
         <v>77</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>380</v>
+        <v>235</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>75</v>
@@ -8720,13 +8784,13 @@
         <v>77</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>383</v>
+        <v>126</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>77</v>
@@ -8737,15 +8801,15 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
-        <v>77</v>
+        <v>408</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>83</v>
@@ -8757,18 +8821,20 @@
         <v>77</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>149</v>
+        <v>409</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>150</v>
+        <v>410</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M62" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
         <v>77</v>
@@ -8817,10 +8883,10 @@
         <v>77</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>152</v>
+        <v>407</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -8829,35 +8895,35 @@
         <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>77</v>
+        <v>412</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>153</v>
+        <v>413</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>77</v>
+        <v>388</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>77</v>
+        <v>414</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F63" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>77</v>
@@ -8869,17 +8935,15 @@
         <v>77</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>130</v>
+        <v>416</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
         <v>77</v>
@@ -8904,13 +8968,13 @@
         <v>77</v>
       </c>
       <c r="W63" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>77</v>
+        <v>418</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>77</v>
+        <v>419</v>
       </c>
       <c r="Z63" t="s" s="2">
         <v>77</v>
@@ -8928,19 +8992,19 @@
         <v>77</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>159</v>
+        <v>415</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>77</v>
@@ -8957,43 +9021,39 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>386</v>
+        <v>420</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F64" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>129</v>
+        <v>421</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>233</v>
+        <v>422</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
         <v>77</v>
       </c>
@@ -9041,25 +9101,25 @@
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>235</v>
+        <v>420</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>126</v>
+        <v>424</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>77</v>
@@ -9068,13 +9128,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="B65" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="C65" t="s" s="2">
-        <v>388</v>
+        <v>77</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9084,7 +9146,7 @@
         <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -9093,17 +9155,15 @@
         <v>84</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>406</v>
+        <v>225</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
         <v>77</v>
@@ -9152,13 +9212,13 @@
         <v>77</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>77</v>
@@ -9167,21 +9227,21 @@
         <v>95</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>392</v>
+        <v>77</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>394</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9204,13 +9264,13 @@
         <v>77</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>396</v>
+        <v>150</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>397</v>
+        <v>151</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -9237,13 +9297,13 @@
         <v>77</v>
       </c>
       <c r="W66" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>398</v>
+        <v>77</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>399</v>
+        <v>77</v>
       </c>
       <c r="Z66" t="s" s="2">
         <v>77</v>
@@ -9261,7 +9321,7 @@
         <v>77</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>395</v>
+        <v>152</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>75</v>
@@ -9273,7 +9333,7 @@
         <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>77</v>
@@ -9290,18 +9350,18 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>77</v>
@@ -9313,15 +9373,17 @@
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>401</v>
+        <v>129</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>402</v>
+        <v>130</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="M67" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
         <v>77</v>
@@ -9370,25 +9432,25 @@
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>400</v>
+        <v>159</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>404</v>
+        <v>153</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>77</v>
@@ -9397,43 +9459,45 @@
         <v>77</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H68" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>225</v>
+        <v>129</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>381</v>
+        <v>233</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O68" t="s" s="2">
         <v>77</v>
       </c>
@@ -9481,7 +9545,7 @@
         <v>77</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>380</v>
+        <v>235</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>75</v>
@@ -9493,13 +9557,13 @@
         <v>77</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>383</v>
+        <v>126</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>77</v>
@@ -9510,15 +9574,15 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
-        <v>77</v>
+        <v>408</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F69" t="s" s="2">
         <v>83</v>
@@ -9530,18 +9594,20 @@
         <v>77</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>149</v>
+        <v>426</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>150</v>
+        <v>410</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M69" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
         <v>77</v>
@@ -9590,10 +9656,10 @@
         <v>77</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>152</v>
+        <v>407</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -9602,35 +9668,35 @@
         <v>77</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>77</v>
+        <v>412</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>153</v>
+        <v>413</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>77</v>
+        <v>388</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>77</v>
+        <v>414</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F70" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>77</v>
@@ -9642,17 +9708,15 @@
         <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>130</v>
+        <v>416</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
         <v>77</v>
@@ -9677,13 +9741,13 @@
         <v>77</v>
       </c>
       <c r="W70" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>77</v>
+        <v>418</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>77</v>
+        <v>419</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>77</v>
@@ -9701,19 +9765,19 @@
         <v>77</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>159</v>
+        <v>415</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>77</v>
@@ -9730,43 +9794,39 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>386</v>
+        <v>420</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>129</v>
+        <v>421</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>233</v>
+        <v>422</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
         <v>77</v>
       </c>
@@ -9814,25 +9874,25 @@
         <v>77</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>235</v>
+        <v>420</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>126</v>
+        <v>424</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>77</v>
@@ -9841,13 +9901,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="B72" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="C72" t="s" s="2">
-        <v>388</v>
+        <v>77</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -9857,7 +9919,7 @@
         <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>77</v>
@@ -9866,17 +9928,15 @@
         <v>84</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>408</v>
+        <v>225</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="M72" s="2"/>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
         <v>77</v>
@@ -9925,13 +9985,13 @@
         <v>77</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>77</v>
@@ -9940,21 +10000,21 @@
         <v>95</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>392</v>
+        <v>77</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>394</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -9977,13 +10037,13 @@
         <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>396</v>
+        <v>150</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>397</v>
+        <v>151</v>
       </c>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
@@ -10010,13 +10070,13 @@
         <v>77</v>
       </c>
       <c r="W73" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>398</v>
+        <v>77</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>399</v>
+        <v>77</v>
       </c>
       <c r="Z73" t="s" s="2">
         <v>77</v>
@@ -10034,7 +10094,7 @@
         <v>77</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>395</v>
+        <v>152</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>75</v>
@@ -10046,7 +10106,7 @@
         <v>77</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>77</v>
@@ -10063,18 +10123,18 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>77</v>
@@ -10086,15 +10146,17 @@
         <v>77</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>401</v>
+        <v>129</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>402</v>
+        <v>130</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="M74" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
         <v>77</v>
@@ -10143,25 +10205,25 @@
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>400</v>
+        <v>159</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>404</v>
+        <v>153</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>77</v>
@@ -10172,11 +10234,11 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10189,24 +10251,26 @@
         <v>77</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>410</v>
+        <v>129</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>411</v>
+        <v>233</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>412</v>
+        <v>234</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O75" t="s" s="2">
         <v>77</v>
       </c>
@@ -10254,7 +10318,7 @@
         <v>77</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>409</v>
+        <v>235</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>75</v>
@@ -10266,13 +10330,13 @@
         <v>77</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>414</v>
+        <v>126</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>77</v>
@@ -10283,15 +10347,15 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>77</v>
+        <v>408</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F76" t="s" s="2">
         <v>83</v>
@@ -10303,19 +10367,19 @@
         <v>77</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>225</v>
+        <v>428</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>418</v>
+        <v>383</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
@@ -10365,10 +10429,10 @@
         <v>77</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -10380,21 +10444,21 @@
         <v>95</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>77</v>
+        <v>412</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>77</v>
+        <v>388</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>77</v>
+        <v>414</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
@@ -10417,13 +10481,13 @@
         <v>77</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>150</v>
+        <v>416</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>151</v>
+        <v>417</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -10450,13 +10514,13 @@
         <v>77</v>
       </c>
       <c r="W77" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>77</v>
+        <v>418</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>77</v>
+        <v>419</v>
       </c>
       <c r="Z77" t="s" s="2">
         <v>77</v>
@@ -10474,7 +10538,7 @@
         <v>77</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>75</v>
@@ -10486,7 +10550,7 @@
         <v>77</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>77</v>
@@ -10503,18 +10567,18 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F78" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>77</v>
@@ -10526,17 +10590,15 @@
         <v>77</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>129</v>
+        <v>421</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>130</v>
+        <v>422</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="M78" s="2"/>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
         <v>77</v>
@@ -10585,25 +10647,25 @@
         <v>77</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>159</v>
+        <v>420</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>153</v>
+        <v>424</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>77</v>
@@ -10614,11 +10676,11 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10631,26 +10693,24 @@
         <v>77</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>129</v>
+        <v>430</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>233</v>
+        <v>431</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>234</v>
+        <v>432</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
         <v>77</v>
       </c>
@@ -10698,7 +10758,7 @@
         <v>77</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>235</v>
+        <v>429</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>75</v>
@@ -10710,13 +10770,13 @@
         <v>77</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>126</v>
+        <v>434</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>77</v>
@@ -10727,7 +10787,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
@@ -10750,15 +10810,17 @@
         <v>77</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>141</v>
+        <v>225</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="M80" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
         <v>77</v>
@@ -10807,7 +10869,7 @@
         <v>77</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>75</v>
@@ -10825,18 +10887,18 @@
         <v>77</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>145</v>
+        <v>439</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>426</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
@@ -10859,13 +10921,13 @@
         <v>77</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>428</v>
+        <v>149</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>429</v>
+        <v>150</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>430</v>
+        <v>151</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -10916,7 +10978,7 @@
         <v>77</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>427</v>
+        <v>152</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>75</v>
@@ -10928,13 +10990,13 @@
         <v>77</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>431</v>
+        <v>153</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>77</v>
@@ -10945,18 +11007,18 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F82" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>77</v>
@@ -10968,15 +11030,17 @@
         <v>77</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>433</v>
+        <v>130</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="M82" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
         <v>77</v>
@@ -11001,13 +11065,13 @@
         <v>77</v>
       </c>
       <c r="W82" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>435</v>
+        <v>77</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>436</v>
+        <v>77</v>
       </c>
       <c r="Z82" t="s" s="2">
         <v>77</v>
@@ -11025,68 +11089,72 @@
         <v>77</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>432</v>
+        <v>159</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>437</v>
+        <v>153</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>438</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>440</v>
+        <v>233</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="M83" s="2"/>
-      <c r="N83" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O83" t="s" s="2">
         <v>77</v>
       </c>
@@ -11110,13 +11178,13 @@
         <v>77</v>
       </c>
       <c r="W83" t="s" s="2">
-        <v>265</v>
+        <v>77</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>442</v>
+        <v>77</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>443</v>
+        <v>77</v>
       </c>
       <c r="Z83" t="s" s="2">
         <v>77</v>
@@ -11134,36 +11202,36 @@
         <v>77</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>439</v>
+        <v>235</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>444</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
@@ -11174,7 +11242,7 @@
         <v>75</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>77</v>
@@ -11186,20 +11254,16 @@
         <v>77</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="M84" s="2"/>
+      <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
         <v>77</v>
       </c>
@@ -11223,13 +11287,13 @@
         <v>77</v>
       </c>
       <c r="W84" t="s" s="2">
-        <v>265</v>
+        <v>77</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>450</v>
+        <v>77</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>451</v>
+        <v>77</v>
       </c>
       <c r="Z84" t="s" s="2">
         <v>77</v>
@@ -11247,13 +11311,13 @@
         <v>77</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>77</v>
@@ -11265,18 +11329,18 @@
         <v>77</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>452</v>
+        <v>145</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>453</v>
+        <v>446</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
@@ -11287,7 +11351,7 @@
         <v>75</v>
       </c>
       <c r="F85" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>77</v>
@@ -11299,13 +11363,13 @@
         <v>77</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>171</v>
+        <v>448</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
@@ -11332,13 +11396,13 @@
         <v>77</v>
       </c>
       <c r="W85" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>457</v>
+        <v>77</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>458</v>
+        <v>77</v>
       </c>
       <c r="Z85" t="s" s="2">
         <v>77</v>
@@ -11356,13 +11420,13 @@
         <v>77</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>77</v>
@@ -11374,18 +11438,18 @@
         <v>77</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>460</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
@@ -11396,7 +11460,7 @@
         <v>75</v>
       </c>
       <c r="F86" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>77</v>
@@ -11411,10 +11475,10 @@
         <v>171</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
@@ -11444,10 +11508,10 @@
         <v>107</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="Z86" t="s" s="2">
         <v>77</v>
@@ -11465,13 +11529,13 @@
         <v>77</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>77</v>
@@ -11483,18 +11547,18 @@
         <v>77</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>467</v>
+        <v>458</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
@@ -11517,13 +11581,13 @@
         <v>77</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>428</v>
+        <v>171</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
@@ -11550,13 +11614,13 @@
         <v>77</v>
       </c>
       <c r="W87" t="s" s="2">
-        <v>77</v>
+        <v>266</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>77</v>
+        <v>462</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>77</v>
+        <v>463</v>
       </c>
       <c r="Z87" t="s" s="2">
         <v>77</v>
@@ -11574,7 +11638,7 @@
         <v>77</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>75</v>
@@ -11592,18 +11656,18 @@
         <v>77</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>471</v>
+        <v>153</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>472</v>
+        <v>464</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
@@ -11614,7 +11678,7 @@
         <v>75</v>
       </c>
       <c r="F88" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>77</v>
@@ -11629,13 +11693,17 @@
         <v>171</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M88" s="2"/>
-      <c r="N88" s="2"/>
+        <v>467</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="O88" t="s" s="2">
         <v>77</v>
       </c>
@@ -11659,13 +11727,13 @@
         <v>77</v>
       </c>
       <c r="W88" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="Z88" t="s" s="2">
         <v>77</v>
@@ -11683,13 +11751,13 @@
         <v>77</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>77</v>
@@ -11701,18 +11769,18 @@
         <v>77</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
@@ -11735,17 +11803,15 @@
         <v>77</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>225</v>
+        <v>171</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
         <v>77</v>
@@ -11770,13 +11836,13 @@
         <v>77</v>
       </c>
       <c r="W89" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>77</v>
+        <v>477</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>77</v>
+        <v>478</v>
       </c>
       <c r="Z89" t="s" s="2">
         <v>77</v>
@@ -11794,7 +11860,7 @@
         <v>77</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="AF89" t="s" s="2">
         <v>75</v>
@@ -11812,18 +11878,18 @@
         <v>77</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>77</v>
+        <v>480</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
@@ -11834,7 +11900,7 @@
         <v>75</v>
       </c>
       <c r="F90" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>77</v>
@@ -11846,13 +11912,13 @@
         <v>77</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>150</v>
+        <v>482</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>151</v>
+        <v>483</v>
       </c>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
@@ -11879,13 +11945,13 @@
         <v>77</v>
       </c>
       <c r="W90" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>77</v>
+        <v>484</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>77</v>
+        <v>485</v>
       </c>
       <c r="Z90" t="s" s="2">
         <v>77</v>
@@ -11903,47 +11969,47 @@
         <v>77</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>152</v>
+        <v>481</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>153</v>
+        <v>486</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>77</v>
+        <v>487</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F91" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>77</v>
@@ -11955,17 +12021,15 @@
         <v>77</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>129</v>
+        <v>448</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>130</v>
+        <v>489</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="M91" s="2"/>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
         <v>77</v>
@@ -12014,72 +12078,68 @@
         <v>77</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>159</v>
+        <v>488</v>
       </c>
       <c r="AF91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>153</v>
+        <v>491</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>77</v>
+        <v>492</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F92" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>233</v>
+        <v>494</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="M92" s="2"/>
+      <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
         <v>77</v>
       </c>
@@ -12103,13 +12163,13 @@
         <v>77</v>
       </c>
       <c r="W92" t="s" s="2">
-        <v>77</v>
+        <v>266</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>77</v>
+        <v>496</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>77</v>
+        <v>497</v>
       </c>
       <c r="Z92" t="s" s="2">
         <v>77</v>
@@ -12127,36 +12187,36 @@
         <v>77</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>235</v>
+        <v>493</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>126</v>
+        <v>498</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>77</v>
+        <v>499</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
@@ -12164,10 +12224,10 @@
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F93" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>77</v>
@@ -12179,15 +12239,17 @@
         <v>77</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>489</v>
+        <v>225</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="M93" s="2"/>
+        <v>502</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
         <v>77</v>
@@ -12236,13 +12298,13 @@
         <v>77</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>77</v>
@@ -12251,21 +12313,21 @@
         <v>95</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>492</v>
+        <v>77</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>335</v>
+        <v>504</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>493</v>
+        <v>77</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>494</v>
+        <v>77</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" t="s" s="2">
@@ -12288,17 +12350,15 @@
         <v>77</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>496</v>
+        <v>150</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>498</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="M94" s="2"/>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
         <v>77</v>
@@ -12323,13 +12383,13 @@
         <v>77</v>
       </c>
       <c r="W94" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>499</v>
+        <v>77</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>500</v>
+        <v>77</v>
       </c>
       <c r="Z94" t="s" s="2">
         <v>77</v>
@@ -12347,7 +12407,7 @@
         <v>77</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>495</v>
+        <v>152</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>75</v>
@@ -12359,13 +12419,13 @@
         <v>77</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>501</v>
+        <v>153</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>77</v>
@@ -12376,18 +12436,18 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F95" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>77</v>
@@ -12399,16 +12459,16 @@
         <v>77</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>503</v>
+        <v>130</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>504</v>
+        <v>155</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>505</v>
+        <v>132</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
@@ -12434,13 +12494,13 @@
         <v>77</v>
       </c>
       <c r="W95" t="s" s="2">
-        <v>265</v>
+        <v>77</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>506</v>
+        <v>77</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>507</v>
+        <v>77</v>
       </c>
       <c r="Z95" t="s" s="2">
         <v>77</v>
@@ -12458,25 +12518,25 @@
         <v>77</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>502</v>
+        <v>159</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>77</v>
@@ -12487,39 +12547,43 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>509</v>
+        <v>233</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="M96" s="2"/>
-      <c r="N96" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O96" t="s" s="2">
         <v>77</v>
       </c>
@@ -12567,25 +12631,25 @@
         <v>77</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>508</v>
+        <v>235</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>328</v>
+        <v>126</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>77</v>
@@ -12596,7 +12660,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
@@ -12604,7 +12668,7 @@
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>83</v>
@@ -12619,13 +12683,13 @@
         <v>77</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>206</v>
+        <v>509</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
@@ -12676,10 +12740,10 @@
         <v>77</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
@@ -12691,21 +12755,21 @@
         <v>95</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>334</v>
+        <v>512</v>
       </c>
       <c r="AK97" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AM97" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>515</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" t="s" s="2">
@@ -12728,16 +12792,16 @@
         <v>77</v>
       </c>
       <c r="J98" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="K98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
@@ -12763,13 +12827,13 @@
         <v>77</v>
       </c>
       <c r="W98" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>77</v>
+        <v>519</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>77</v>
+        <v>520</v>
       </c>
       <c r="Z98" t="s" s="2">
         <v>77</v>
@@ -12787,7 +12851,7 @@
         <v>77</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AF98" t="s" s="2">
         <v>75</v>
@@ -12802,20 +12866,460 @@
         <v>95</v>
       </c>
       <c r="AJ98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK98" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AK98" t="s" s="2">
+      <c r="AL98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AL98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM98" t="s" s="2">
+      <c r="B99" s="2"/>
+      <c r="C99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D99" s="2"/>
+      <c r="E99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P99" s="2"/>
+      <c r="Q99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B100" s="2"/>
+      <c r="C100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D100" s="2"/>
+      <c r="E100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M100" s="2"/>
+      <c r="N100" s="2"/>
+      <c r="O100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P100" s="2"/>
+      <c r="Q100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B101" s="2"/>
+      <c r="C101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D101" s="2"/>
+      <c r="E101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M101" s="2"/>
+      <c r="N101" s="2"/>
+      <c r="O101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P101" s="2"/>
+      <c r="Q101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B102" s="2"/>
+      <c r="C102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D102" s="2"/>
+      <c r="E102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P102" s="2"/>
+      <c r="Q102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM98">
+  <autoFilter ref="A1:AM102">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12825,7 +13329,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI97">
+  <conditionalFormatting sqref="A2:AI101">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T17:11:36+00:00</t>
+    <t>2023-03-10T20:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterAtenderLE.xlsx
+++ b/StructureDefinition-EncounterAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T20:13:24+00:00</t>
+    <t>2023-03-11T11:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
